--- a/data/trans_orig/P6907S1-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6907S1-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8639</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10837</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34205</t>
+          <t>33908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41871</t>
+          <t>41882</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>23056</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60626</t>
+          <t>60262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69546</t>
+          <t>69552</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13844</t>
+          <t>14450</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15922</t>
+          <t>16350</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58553</t>
+          <t>57947</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70504</t>
+          <t>70502</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26022</t>
+          <t>26683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>89162</t>
+          <t>88734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>102039</t>
+          <t>102115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>8571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>11186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27606</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35643</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46455</t>
+          <t>47153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56336</t>
+          <t>56356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12399</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48764</t>
+          <t>48242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57277</t>
+          <t>57304</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>16412</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>68630</t>
+          <t>68458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78461</t>
+          <t>78902</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>6777</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9884</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>16177</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22091</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>28042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12134</t>
+          <t>11978</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>13345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29676</t>
+          <t>29832</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39726</t>
+          <t>39713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43115</t>
+          <t>42558</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53073</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>19614</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12365</t>
+          <t>12261</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10044</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26206</t>
+          <t>27484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68456</t>
+          <t>68834</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82920</t>
+          <t>82905</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31170</t>
+          <t>31274</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40713</t>
+          <t>40582</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>105777</t>
+          <t>104499</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>121939</t>
+          <t>121887</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,35%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>22702</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>96172</t>
+          <t>95995</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>106091</t>
+          <t>106211</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36739</t>
+          <t>35997</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46699</t>
+          <t>45736</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136583</t>
+          <t>135999</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>150784</t>
+          <t>150840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>32292</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>57283</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>15931</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34298</t>
+          <t>35361</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>84638</t>
+          <t>84594</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>415022</t>
+          <t>414413</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>440931</t>
+          <t>440013</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>185823</t>
+          <t>184760</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>203976</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>607833</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>640204</t>
+          <t>640300</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2012 (tasa de respuesta: 44,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,62 +4091,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4732</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4495</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14149</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25690</t>
+          <t>25453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34415</t>
+          <t>34389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,62 +4777,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1614</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5050</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>5045</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12788</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10443</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5900</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,62 +5463,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6306</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>10,35%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>6757</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8783</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,97 +5771,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1811</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20933</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>29439</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6114,97 +6114,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>4914</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>947</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4143</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4750</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>5240</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24094</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25998</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>23332</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>49494</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,62 +6492,62 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1919</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>6853</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11309</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13228</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>28911</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>128713</t>
+          <t>127469</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138749</t>
+          <t>138869</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>92422</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>99260</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>224361</t>
+          <t>223952</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>237048</t>
+          <t>237271</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>8230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>11867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50304</t>
+          <t>50211</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57675</t>
+          <t>57667</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33155</t>
+          <t>32654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>87000</t>
+          <t>87594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97585</t>
+          <t>97439</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,97%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74092</t>
+          <t>74087</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>81786</t>
+          <t>81774</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116987</t>
+          <t>116908</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124475</t>
+          <t>124464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>16943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,47 +8443,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1902</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>898</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27823</t>
+          <t>27063</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29935</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57811</t>
+          <t>57816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8751,97 +8751,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1525</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1960</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18681</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20641</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>6154</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,62 +9129,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1938</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1727</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6155</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1938</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5820</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>23705</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>10388</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>69867</t>
+          <t>70416</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>49256</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>124419</t>
+          <t>123636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>132922</t>
+          <t>132920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9780,97 +9780,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>9,05%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37300</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19464</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21400</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>58672</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60674</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>328911</t>
+          <t>329642</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>343179</t>
+          <t>343846</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>204528</t>
+          <t>203460</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>214425</t>
+          <t>214384</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>539343</t>
+          <t>537290</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>555555</t>
+          <t>555834</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4230</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>170</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19839</t>
+          <t>19788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11621</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>15585</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>33648</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39156</t>
+          <t>39140</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6153</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>35241</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46280</t>
+          <t>45119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39290</t>
+          <t>39384</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44715</t>
+          <t>44727</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78901</t>
+          <t>78944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89307</t>
+          <t>89447</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4407</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13033</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>22555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36312</t>
+          <t>36336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45888</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32893</t>
+          <t>33460</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41419</t>
+          <t>41519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72902</t>
+          <t>72867</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85676</t>
+          <t>85743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16039</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4061</t>
+          <t>3945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18807</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24314</t>
+          <t>26241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76591</t>
+          <t>76707</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>102198</t>
+          <t>103968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120274</t>
+          <t>120393</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,62 +12109,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2921</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3093</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>15033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10264</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25650</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13374</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>467</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5038</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>15687</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18282</t>
+          <t>18242</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27394</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25726</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29760</t>
+          <t>29748</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>46144</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>56611</t>
+          <t>56793</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19297</t>
+          <t>19555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>22337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15853</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35687</t>
+          <t>34374</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53881</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66655</t>
+          <t>67540</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49314</t>
+          <t>48190</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>63275</t>
+          <t>62575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>108018</t>
+          <t>109331</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127852</t>
+          <t>128443</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -13103,97 +13103,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1731</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5723</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>10,46%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>1731</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5944</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>6654</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>10,86%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1731</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>6176</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>54884</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56757</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48766</t>
+          <t>48987</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105291</t>
+          <t>104813</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26759</t>
+          <t>26360</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>51777</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>19415</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41055</t>
+          <t>41707</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>49477</t>
+          <t>50220</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>83611</t>
+          <t>84552</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>288211</t>
+          <t>287728</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>312746</t>
+          <t>313145</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>313160</t>
+          <t>312508</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>335022</t>
+          <t>334800</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>610109</t>
+          <t>609168</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>644243</t>
+          <t>643500</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
